--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
@@ -400,22 +400,22 @@
         <v>0.7325767622515603</v>
       </c>
       <c r="C2">
-        <v>0.7428738266081906</v>
+        <v>0.7506371350073703</v>
       </c>
       <c r="D2">
         <v>1.594702201724019</v>
       </c>
       <c r="E2">
-        <v>0.7524358076969213</v>
+        <v>0.7522860507893896</v>
       </c>
       <c r="F2">
         <v>0.7470683357879488</v>
       </c>
       <c r="G2">
-        <v>0.7747833279462306</v>
+        <v>0.7685891331095891</v>
       </c>
       <c r="H2">
-        <v>0.7529190144724247</v>
+        <v>0.7527649057129348</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -426,22 +426,22 @@
         <v>0.7565117611137623</v>
       </c>
       <c r="C3">
-        <v>0.7463819025479502</v>
+        <v>0.7560526663458433</v>
       </c>
       <c r="D3">
         <v>1.531761101935835</v>
       </c>
       <c r="E3">
-        <v>0.7564170359425745</v>
+        <v>0.7562245264861476</v>
       </c>
       <c r="F3">
         <v>0.7622186643604321</v>
       </c>
       <c r="G3">
-        <v>0.7770276209792533</v>
+        <v>0.7708789861869617</v>
       </c>
       <c r="H3">
-        <v>0.756687626972869</v>
+        <v>0.7564955692110905</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -452,22 +452,22 @@
         <v>0.6837215924857288</v>
       </c>
       <c r="C4">
-        <v>0.7699562596260292</v>
+        <v>0.7512958322845921</v>
       </c>
       <c r="D4">
         <v>1.170512505105007</v>
       </c>
       <c r="E4">
-        <v>0.7467924631479942</v>
+        <v>0.7465967585015808</v>
       </c>
       <c r="F4">
         <v>0.7012780821354155</v>
       </c>
       <c r="G4">
-        <v>0.7582039047428399</v>
+        <v>0.7464637078808254</v>
       </c>
       <c r="H4">
-        <v>0.7469217645471885</v>
+        <v>0.7467258612804342</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -478,22 +478,22 @@
         <v>0.7920320214721451</v>
       </c>
       <c r="C5">
-        <v>0.7962487799499285</v>
+        <v>0.7843231854640947</v>
       </c>
       <c r="D5">
         <v>0.4105244968136729</v>
       </c>
       <c r="E5">
-        <v>0.763918153379728</v>
+        <v>0.7636218546345843</v>
       </c>
       <c r="F5">
         <v>0.7844444256025577</v>
       </c>
       <c r="G5">
-        <v>0.7817840426466831</v>
+        <v>0.7764259826412993</v>
       </c>
       <c r="H5">
-        <v>0.7637190368229271</v>
+        <v>0.7634235085331788</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -504,22 +504,22 @@
         <v>0.7829951580196046</v>
       </c>
       <c r="C6">
-        <v>0.7947192688087488</v>
+        <v>0.7814385392731652</v>
       </c>
       <c r="D6">
         <v>0.2511295960563111</v>
       </c>
       <c r="E6">
-        <v>0.7625457610805318</v>
+        <v>0.762250841063698</v>
       </c>
       <c r="F6">
         <v>0.7763724083021228</v>
       </c>
       <c r="G6">
-        <v>0.7760571709281976</v>
+        <v>0.7706515248517226</v>
       </c>
       <c r="H6">
-        <v>0.7622870694416859</v>
+        <v>0.7619929015327521</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -530,22 +530,22 @@
         <v>0.8015667912701183</v>
       </c>
       <c r="C7">
-        <v>0.7993966827599528</v>
+        <v>0.7894287252199673</v>
       </c>
       <c r="D7">
         <v>0.3828568701346464</v>
       </c>
       <c r="E7">
-        <v>0.7644317724559087</v>
+        <v>0.7641379473065246</v>
       </c>
       <c r="F7">
         <v>0.7937910582919011</v>
       </c>
       <c r="G7">
-        <v>0.7826180338824664</v>
+        <v>0.7806982292143918</v>
       </c>
       <c r="H7">
-        <v>0.764221243538187</v>
+        <v>0.7639281902307521</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -556,22 +556,22 @@
         <v>0.7449368387269226</v>
       </c>
       <c r="C8">
-        <v>0.7180895215873215</v>
+        <v>0.7281542421987869</v>
       </c>
       <c r="D8">
         <v>0.3144157603848184</v>
       </c>
       <c r="E8">
-        <v>0.7431321011672083</v>
+        <v>0.7435263617765947</v>
       </c>
       <c r="F8">
         <v>0.7382069388759523</v>
       </c>
       <c r="G8">
-        <v>0.71399605079497</v>
+        <v>0.7251023143756458</v>
       </c>
       <c r="H8">
-        <v>0.742960681489826</v>
+        <v>0.7433554189163866</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -582,22 +582,22 @@
         <v>0.8082516464155737</v>
       </c>
       <c r="C9">
-        <v>0.7749148947119088</v>
+        <v>0.7673968131939678</v>
       </c>
       <c r="D9">
         <v>0.4907369594154016</v>
       </c>
       <c r="E9">
-        <v>0.7627814978018569</v>
+        <v>0.7625033032669952</v>
       </c>
       <c r="F9">
         <v>0.8008314410081749</v>
       </c>
       <c r="G9">
-        <v>0.763268773452269</v>
+        <v>0.7631747969005328</v>
       </c>
       <c r="H9">
-        <v>0.7626641276885489</v>
+        <v>0.762386454026641</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -608,22 +608,22 @@
         <v>0.7901193396688405</v>
       </c>
       <c r="C10">
-        <v>0.796455973792794</v>
+        <v>0.7856474367023336</v>
       </c>
       <c r="D10">
         <v>1.371529122152553</v>
       </c>
       <c r="E10">
-        <v>0.7627957419852761</v>
+        <v>0.7625549981841466</v>
       </c>
       <c r="F10">
         <v>0.7924859041778979</v>
       </c>
       <c r="G10">
-        <v>0.7998265137805515</v>
+        <v>0.7899586053769507</v>
       </c>
       <c r="H10">
-        <v>0.763161247005138</v>
+        <v>0.7629209925256918</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -634,22 +634,22 @@
         <v>0.7824232959475607</v>
       </c>
       <c r="C11">
-        <v>0.797663049898691</v>
+        <v>0.7898377149511048</v>
       </c>
       <c r="D11">
         <v>1.251478324715245</v>
       </c>
       <c r="E11">
-        <v>0.7634202320927728</v>
+        <v>0.7631940235267909</v>
       </c>
       <c r="F11">
         <v>0.784691742817359</v>
       </c>
       <c r="G11">
-        <v>0.7979297844464777</v>
+        <v>0.7877220119822033</v>
       </c>
       <c r="H11">
-        <v>0.7636471422987593</v>
+        <v>0.7634211177787166</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -660,22 +660,22 @@
         <v>0.6650539704803021</v>
       </c>
       <c r="C12">
-        <v>0.7987059996499829</v>
+        <v>0.7812697644724856</v>
       </c>
       <c r="D12">
-        <v>0.6630645759324548</v>
+        <v>0.663064575932455</v>
       </c>
       <c r="E12">
-        <v>0.7571573853816395</v>
+        <v>0.7568676496393121</v>
       </c>
       <c r="F12">
         <v>0.6770459255562024</v>
       </c>
       <c r="G12">
-        <v>0.7826881838904574</v>
+        <v>0.7733773858512553</v>
       </c>
       <c r="H12">
-        <v>0.7569472511483959</v>
+        <v>0.756658300858177</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -686,22 +686,22 @@
         <v>0.7853295825320202</v>
       </c>
       <c r="C13">
-        <v>0.7956510506313477</v>
+        <v>0.7838646314813464</v>
       </c>
       <c r="D13">
         <v>1.200349245239656</v>
       </c>
       <c r="E13">
-        <v>0.7619929502133752</v>
+        <v>0.7617501679752831</v>
       </c>
       <c r="F13">
         <v>0.7864898091764774</v>
       </c>
       <c r="G13">
-        <v>0.7951664937103869</v>
+        <v>0.7852402058903404</v>
       </c>
       <c r="H13">
-        <v>0.7622543408450436</v>
+        <v>0.7620120126676011</v>
       </c>
     </row>
   </sheetData>

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>Zone</t>
   </si>
@@ -28,7 +28,10 @@
     <t>OV</t>
   </si>
   <si>
-    <t>Auto-FietsOV_Fiets</t>
+    <t>Auto-Fiets</t>
+  </si>
+  <si>
+    <t>OV_Fiets</t>
   </si>
   <si>
     <t>Auto_OV</t>
@@ -391,6 +394,9 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
       <c r="A2">

--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/arbeidsplaatsen/restdag/Ontpl_conc_hoog.xlsx
@@ -403,25 +403,25 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0.7325767622515603</v>
+        <v>0.3941701649633306</v>
       </c>
       <c r="C2">
-        <v>0.7506371350073703</v>
+        <v>0.4038877269654029</v>
       </c>
       <c r="D2">
-        <v>1.594702201724019</v>
+        <v>0.858045275677326</v>
       </c>
       <c r="E2">
-        <v>0.7522860507893896</v>
+        <v>0.404774942393601</v>
       </c>
       <c r="F2">
-        <v>0.7470683357879488</v>
+        <v>0.4019674992848019</v>
       </c>
       <c r="G2">
-        <v>0.7685891331095891</v>
+        <v>0.4135469769143428</v>
       </c>
       <c r="H2">
-        <v>0.7527649057129348</v>
+        <v>0.405032595016416</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -429,25 +429,25 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>0.7565117611137623</v>
+        <v>0.5759350230230638</v>
       </c>
       <c r="C3">
-        <v>0.7560526663458433</v>
+        <v>0.575585512586713</v>
       </c>
       <c r="D3">
-        <v>1.531761101935835</v>
+        <v>1.166135030353595</v>
       </c>
       <c r="E3">
-        <v>0.7562245264861476</v>
+        <v>0.5757163503065619</v>
       </c>
       <c r="F3">
-        <v>0.7622186643604321</v>
+        <v>0.5802797082238891</v>
       </c>
       <c r="G3">
-        <v>0.7708789861869617</v>
+        <v>0.5868728412152472</v>
       </c>
       <c r="H3">
-        <v>0.7564955692110905</v>
+        <v>0.5759226960714982</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -455,25 +455,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0.6837215924857288</v>
+        <v>0.4306726325720635</v>
       </c>
       <c r="C4">
-        <v>0.7512958322845921</v>
+        <v>0.4732372905674737</v>
       </c>
       <c r="D4">
-        <v>1.170512505105007</v>
+        <v>0.7372996663735116</v>
       </c>
       <c r="E4">
-        <v>0.7465967585015808</v>
+        <v>0.4702773687235219</v>
       </c>
       <c r="F4">
-        <v>0.7012780821354155</v>
+        <v>0.4417313729998239</v>
       </c>
       <c r="G4">
-        <v>0.7464637078808254</v>
+        <v>0.4701935608377747</v>
       </c>
       <c r="H4">
-        <v>0.7467258612804342</v>
+        <v>0.4703586898844337</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -481,25 +481,25 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0.7920320214721451</v>
+        <v>0.1986210332484327</v>
       </c>
       <c r="C5">
-        <v>0.7843231854640947</v>
+        <v>0.1966878576550826</v>
       </c>
       <c r="D5">
-        <v>0.4105244968136729</v>
+        <v>0.1029488676220047</v>
       </c>
       <c r="E5">
-        <v>0.7636218546345843</v>
+        <v>0.1914965022458245</v>
       </c>
       <c r="F5">
-        <v>0.7844444256025577</v>
+        <v>0.1967182615288147</v>
       </c>
       <c r="G5">
-        <v>0.7764259826412993</v>
+        <v>0.1947074445632979</v>
       </c>
       <c r="H5">
-        <v>0.7634235085331788</v>
+        <v>0.1914467622018188</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -507,25 +507,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0.7829951580196046</v>
+        <v>0.8931737198120534</v>
       </c>
       <c r="C6">
-        <v>0.7814385392731652</v>
+        <v>0.8913980626552414</v>
       </c>
       <c r="D6">
-        <v>0.2511295960563111</v>
+        <v>0.2864671041285006</v>
       </c>
       <c r="E6">
-        <v>0.762250841063698</v>
+        <v>0.8695103822413202</v>
       </c>
       <c r="F6">
-        <v>0.7763724083021228</v>
+        <v>0.8856190549588139</v>
       </c>
       <c r="G6">
-        <v>0.7706515248517226</v>
+        <v>0.8790931617911869</v>
       </c>
       <c r="H6">
-        <v>0.7619929015327521</v>
+        <v>0.869216146947549</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -533,25 +533,25 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0.8015667912701183</v>
+        <v>0.6345737097555103</v>
       </c>
       <c r="C7">
-        <v>0.7894287252199673</v>
+        <v>0.6249644074658074</v>
       </c>
       <c r="D7">
-        <v>0.3828568701346464</v>
+        <v>0.3030950221899285</v>
       </c>
       <c r="E7">
-        <v>0.7641379473065246</v>
+        <v>0.6049425416176654</v>
       </c>
       <c r="F7">
-        <v>0.7937910582919011</v>
+        <v>0.6284179211477552</v>
       </c>
       <c r="G7">
-        <v>0.7806982292143918</v>
+        <v>0.618052764794727</v>
       </c>
       <c r="H7">
-        <v>0.7639281902307521</v>
+        <v>0.6047764839326789</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -559,25 +559,25 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>0.7449368387269226</v>
+        <v>0.1861776551084899</v>
       </c>
       <c r="C8">
-        <v>0.7281542421987869</v>
+        <v>0.1819832800879447</v>
       </c>
       <c r="D8">
-        <v>0.3144157603848184</v>
+        <v>0.07858007008706515</v>
       </c>
       <c r="E8">
-        <v>0.7435263617765947</v>
+        <v>0.1858251429523649</v>
       </c>
       <c r="F8">
-        <v>0.7382069388759523</v>
+        <v>0.1844956910704248</v>
       </c>
       <c r="G8">
-        <v>0.7251023143756458</v>
+        <v>0.1812205298302935</v>
       </c>
       <c r="H8">
-        <v>0.7433554189163866</v>
+        <v>0.185782420215058</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -585,25 +585,25 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>0.8082516464155737</v>
+        <v>0.5636679019934275</v>
       </c>
       <c r="C9">
-        <v>0.7673968131939678</v>
+        <v>0.5351760848342041</v>
       </c>
       <c r="D9">
-        <v>0.4907369594154016</v>
+        <v>0.3422358291146481</v>
       </c>
       <c r="E9">
-        <v>0.7625033032669952</v>
+        <v>0.5317633921584101</v>
       </c>
       <c r="F9">
-        <v>0.8008314410081749</v>
+        <v>0.5584931131354064</v>
       </c>
       <c r="G9">
-        <v>0.7631747969005328</v>
+        <v>0.5322316861721581</v>
       </c>
       <c r="H9">
-        <v>0.762386454026641</v>
+        <v>0.5316819024807189</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -611,25 +611,25 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>0.7901193396688405</v>
+        <v>0.1963880439639315</v>
       </c>
       <c r="C10">
-        <v>0.7856474367023336</v>
+        <v>0.1952765305098286</v>
       </c>
       <c r="D10">
-        <v>1.371529122152553</v>
+        <v>0.3409003020379177</v>
       </c>
       <c r="E10">
-        <v>0.7625549981841466</v>
+        <v>0.1895367914561752</v>
       </c>
       <c r="F10">
-        <v>0.7924859041778979</v>
+        <v>0.1969762652002868</v>
       </c>
       <c r="G10">
-        <v>0.7899586053769507</v>
+        <v>0.1963480926659473</v>
       </c>
       <c r="H10">
-        <v>0.7629209925256918</v>
+        <v>0.1896277611480043</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -637,25 +637,25 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>0.7824232959475607</v>
+        <v>0.2019156892767898</v>
       </c>
       <c r="C11">
-        <v>0.7898377149511048</v>
+        <v>0.2038290877293174</v>
       </c>
       <c r="D11">
-        <v>1.251478324715245</v>
+        <v>0.3229621483136118</v>
       </c>
       <c r="E11">
-        <v>0.7631940235267909</v>
+        <v>0.1969532963940105</v>
       </c>
       <c r="F11">
-        <v>0.784691742817359</v>
+        <v>0.2025010949206087</v>
       </c>
       <c r="G11">
-        <v>0.7877220119822033</v>
+        <v>0.203283099866375</v>
       </c>
       <c r="H11">
-        <v>0.7634211177787166</v>
+        <v>0.1970119013622495</v>
       </c>
     </row>
     <row r="12" spans="1:8">
@@ -663,25 +663,25 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>0.6650539704803021</v>
+        <v>0.8714905854795397</v>
       </c>
       <c r="C12">
-        <v>0.7812697644724856</v>
+        <v>1.023780436895768</v>
       </c>
       <c r="D12">
-        <v>0.663064575932455</v>
+        <v>0.8688836713098501</v>
       </c>
       <c r="E12">
-        <v>0.7568676496393121</v>
+        <v>0.9918037638935102</v>
       </c>
       <c r="F12">
-        <v>0.6770459255562024</v>
+        <v>0.8872049130589887</v>
       </c>
       <c r="G12">
-        <v>0.7733773858512553</v>
+        <v>1.013438218112418</v>
       </c>
       <c r="H12">
-        <v>0.756658300858177</v>
+        <v>0.991529432034836</v>
       </c>
     </row>
     <row r="13" spans="1:8">
@@ -689,25 +689,25 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>0.7853295825320202</v>
+        <v>0.197339228431123</v>
       </c>
       <c r="C13">
-        <v>0.7838646314813464</v>
+        <v>0.1969711125260819</v>
       </c>
       <c r="D13">
-        <v>1.200349245239656</v>
+        <v>0.3016262205986827</v>
       </c>
       <c r="E13">
-        <v>0.7617501679752831</v>
+        <v>0.1914141447732763</v>
       </c>
       <c r="F13">
-        <v>0.7864898091764774</v>
+        <v>0.1976307725622943</v>
       </c>
       <c r="G13">
-        <v>0.7852402058903404</v>
+        <v>0.1973167696852651</v>
       </c>
       <c r="H13">
-        <v>0.7620120126676011</v>
+        <v>0.1914799416446793</v>
       </c>
     </row>
   </sheetData>
